--- a/myprojects/GatiGo/BvsA/GatiGo_Analystt_Dashboard.xlsx
+++ b/myprojects/GatiGo/BvsA/GatiGo_Analystt_Dashboard.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\inakm.github.io\myprojects\GatiGo\BvsA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="291">
   <si>
     <t>KPI Metric</t>
   </si>
@@ -614,9 +614,6 @@
     <t>Base vs Q1 Δ</t>
   </si>
   <si>
-    <t>── ASSUMPTION INPUTS (edit blue cells) ──</t>
-  </si>
-  <si>
     <t>Daily Rides (avg)</t>
   </si>
   <si>
@@ -821,9 +818,6 @@
     <t>GatiGo  |  Budget vs Actuals Analyst Dashboard  |  Documentation &amp; Credits</t>
   </si>
   <si>
-    <t>This workbook demonstrates professional FP&amp;A analysis, unit economics, and business storytelling for a startup financial model.</t>
-  </si>
-  <si>
     <t>ABOUT THIS PROJECT</t>
   </si>
   <si>
@@ -894,18 +888,6 @@
   </si>
   <si>
     <t>📋 Raw Data  |  📊 Variance Analysis  |  📐 Unit Economics  |  🎯 Scenario Analysis  |  💡 Insights &amp; Recommendations  |  📈 KPI Dashboard  |  ℹ️ About</t>
-  </si>
-  <si>
-    <t>Tools Used</t>
-  </si>
-  <si>
-    <t>Microsoft Excel (openpyxl)  |  Python  |  Financial Modelling Best Practices  |  FP&amp;A Frameworks</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Q1 FY2026 v1.0  —  March 2026</t>
   </si>
   <si>
     <t>⚠  ACADEMIC PROJECT DISCLAIMER
@@ -919,6 +901,9 @@
   </si>
   <si>
     <t>GatiGo  |  KPI Dashboard  |  Q1 FY2026 : Visual Variance Analysis</t>
+  </si>
+  <si>
+    <t>── ASSUMPTION INPUTS ──</t>
   </si>
 </sst>
 </file>
@@ -1329,48 +1314,6 @@
   </cellStyleXfs>
   <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1662,34 +1605,76 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2027,11 +2012,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="297220656"/>
-        <c:axId val="297221440"/>
+        <c:axId val="309912672"/>
+        <c:axId val="240596656"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="297220656"/>
+        <c:axId val="309912672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2099,7 +2084,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="297221440"/>
+        <c:crossAx val="240596656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2107,7 +2092,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="297221440"/>
+        <c:axId val="240596656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2185,7 +2170,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="297220656"/>
+        <c:crossAx val="309912672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2514,11 +2499,11 @@
         </c:hiLowLines>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="297222224"/>
-        <c:axId val="297222616"/>
+        <c:axId val="238912616"/>
+        <c:axId val="312372672"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="297222224"/>
+        <c:axId val="238912616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2586,7 +2571,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="297222616"/>
+        <c:crossAx val="312372672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2594,7 +2579,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="297222616"/>
+        <c:axId val="312372672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2672,7 +2657,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="297222224"/>
+        <c:crossAx val="238912616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2931,6 +2916,9 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -2953,6 +2941,9 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -2975,6 +2966,9 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -2997,6 +2991,9 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -3019,6 +3016,9 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
@@ -3041,6 +3041,9 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="6"/>
@@ -3063,6 +3066,9 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              </c:extLst>
             </c:dLbl>
             <c:spPr>
               <a:noFill/>
@@ -3472,11 +3478,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="237637504"/>
-        <c:axId val="237638680"/>
+        <c:axId val="312464904"/>
+        <c:axId val="312465288"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="237637504"/>
+        <c:axId val="312464904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3509,7 +3515,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="237638680"/>
+        <c:crossAx val="312465288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3517,7 +3523,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="237638680"/>
+        <c:axId val="312465288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3560,7 +3566,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="237637504"/>
+        <c:crossAx val="312464904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3934,504 +3940,504 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="A1" s="102" t="s">
+        <v>289</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
+      <c r="A2" s="103" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="4">
         <v>4680</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="4">
         <v>4800</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="4">
         <v>5980</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="5">
         <f>SUM(B4:D4)</f>
         <v>15460</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21">
+      <c r="F4" s="6"/>
+      <c r="G4" s="7">
         <v>5460</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="7">
         <v>5760</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="7">
         <v>7020</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="8">
         <f>SUM(G4:I4)</f>
         <v>18240</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="9">
         <v>179775</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="9">
         <v>223229</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="9">
         <v>267860</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="10">
         <f>SUM(B5:D5)</f>
         <v>670864</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="25">
+      <c r="F5" s="6"/>
+      <c r="G5" s="11">
         <v>225699</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="11">
         <v>278772</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="11">
         <v>355500</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="12">
         <f>SUM(G5:I5)</f>
         <v>859971</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="9">
         <v>-98265</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="9">
         <v>-68671</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="9">
         <v>-63040</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="10">
         <f>SUM(B6:D6)</f>
         <v>-229976</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="25">
+      <c r="F6" s="6"/>
+      <c r="G6" s="11">
         <v>-98681</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="11">
         <v>-69008</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="11">
         <v>-37940</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="12">
         <f>SUM(G6:I6)</f>
         <v>-205629</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="13">
         <v>-0.54659991656236995</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="13">
         <v>-0.30762580130717798</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="13">
         <v>-0.23534682296722201</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="14">
         <f>AVERAGE(B7:D7)</f>
         <v>-0.36319084694559001</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="29">
+      <c r="F7" s="6"/>
+      <c r="G7" s="15">
         <v>-0.43722391326501198</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="15">
         <v>-0.247542794828749</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="15">
         <v>-0.106722925457103</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="16">
         <f>AVERAGE(G7:I7)</f>
         <v>-0.263829877850288</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="18">
         <v>-561265</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="18">
         <v>-549671</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="18">
         <v>-580040</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="18">
         <f>SUM(B8:D8)</f>
         <v>-1690976</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="33">
+      <c r="F8" s="6"/>
+      <c r="G8" s="19">
         <v>-539681</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="19">
         <v>-517008</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="19">
         <v>-493940</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="20">
         <f>SUM(G8:I8)</f>
         <v>-1550629</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="21">
         <v>-3.1220414406897499</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="21">
         <v>-2.4623637609808799</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="21">
         <v>-2.1654595684312699</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="21">
         <f>AVERAGE(B9:D9)</f>
         <v>-2.5832882567006332</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="36">
+      <c r="F9" s="6"/>
+      <c r="G9" s="22">
         <v>-2.3911537047129099</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="22">
         <v>-1.85459084843528</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="22">
         <v>-1.38942334739803</v>
       </c>
-      <c r="J9" s="37">
+      <c r="J9" s="23">
         <f>AVERAGE(G9:I9)</f>
         <v>-1.8783893001820733</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="9">
         <v>-577265</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="9">
         <v>-565671</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="9">
         <v>-596040</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="10">
         <f>SUM(B10:D10)</f>
         <v>-1738976</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="25">
+      <c r="F10" s="6"/>
+      <c r="G10" s="11">
         <v>-555681</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="11">
         <v>-533008</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="11">
         <v>-509940</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="12">
         <f>SUM(G10:I10)</f>
         <v>-1598629</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="9">
         <v>38.4</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="9">
         <v>46.5</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="9">
         <v>44.8</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="10">
         <f>SUM(B11:D11)</f>
         <v>129.69999999999999</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="25">
+      <c r="F11" s="6"/>
+      <c r="G11" s="11">
         <v>41.3</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="11">
         <v>48.4</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="11">
         <v>50.6</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="12">
         <f>SUM(G11:I11)</f>
         <v>140.29999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="18">
         <v>-21</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="18">
         <v>-14.3</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="18">
         <v>-10.5</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="18">
         <f>SUM(B12:D12)</f>
         <v>-45.8</v>
       </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="33">
+      <c r="F12" s="6"/>
+      <c r="G12" s="19">
         <v>-18.100000000000001</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="19">
         <v>-12</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="19">
         <v>-5.4</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="20">
         <f>SUM(G12:I12)</f>
         <v>-35.5</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="9">
         <v>479000</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="9">
         <v>497000</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="9">
         <v>533000</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="10">
         <f>SUM(B13:D13)</f>
         <v>1509000</v>
       </c>
-      <c r="F13" s="20"/>
-      <c r="G13" s="25">
+      <c r="F13" s="6"/>
+      <c r="G13" s="11">
         <v>457000</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="11">
         <v>464000</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="11">
         <v>472000</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="12">
         <f>SUM(G13:I13)</f>
         <v>1393000</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="13">
         <v>4.1220414406897499</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="13">
         <v>3.4623637609808799</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="13">
         <v>3.1654595684312699</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="14">
         <f>AVERAGE(B14:D14)</f>
         <v>3.5832882567006332</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="29">
+      <c r="F14" s="6"/>
+      <c r="G14" s="15">
         <v>3.3911537047129099</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="15">
         <v>2.8545908484352802</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="15">
         <v>2.3894233473980302</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="16">
         <f>AVERAGE(G14:I14)</f>
         <v>2.8783893001820737</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="13">
         <v>0</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="13">
         <v>0.2417</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="13">
         <v>0.19989999999999999</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="14">
         <f>AVERAGE(B15:D15)</f>
         <v>0.1472</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="29">
+      <c r="F15" s="6"/>
+      <c r="G15" s="15">
         <v>0</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="15">
         <v>0.2351</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="15">
         <v>0.2752</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="16">
         <f>AVERAGE(G15:I15)</f>
         <v>0.1701</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="13">
         <v>0</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="13">
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="13">
         <v>0.24579999999999999</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="14">
         <f>AVERAGE(B16:D16)</f>
         <v>9.0466666666666654E-2</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="29">
+      <c r="F16" s="6"/>
+      <c r="G16" s="15">
         <v>0</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="15">
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="15">
         <v>0.21879999999999999</v>
       </c>
-      <c r="J16" s="30">
+      <c r="J16" s="16">
         <f>AVERAGE(G16:I16)</f>
         <v>9.1233333333333333E-2</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
     </row>
     <row r="18" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
+      <c r="A18" s="104" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" s="104"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -4446,92 +4452,92 @@
       <c r="D19" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="40">
+      <c r="B20" s="26">
         <f>B5</f>
         <v>179775</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="26">
         <f>C5</f>
         <v>223229</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="26">
         <v>267860</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="40">
+      <c r="B21" s="26">
         <v>225699</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="26">
         <v>278772</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="26">
         <v>355500</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="26">
         <v>-561265</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="26">
         <v>-549671</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="26">
         <v>-580040</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="40">
+      <c r="B23" s="26">
         <v>-539681</v>
       </c>
-      <c r="C23" s="40">
+      <c r="C23" s="26">
         <v>-517008</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="26">
         <v>-493940</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="26">
         <v>-577265</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="26">
         <v>-565671</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="26">
         <v>-596040</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="40">
+      <c r="B25" s="26">
         <v>-555681</v>
       </c>
-      <c r="C25" s="40">
+      <c r="C25" s="26">
         <v>-533008</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="26">
         <v>-509940</v>
       </c>
     </row>
@@ -4544,58 +4550,58 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="40">
+      <c r="B28" s="26">
         <v>750960</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="26">
         <v>795000</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
+      <c r="A30" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="26">
         <v>330000</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="26">
         <v>149880</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="40">
+      <c r="B32" s="26">
         <v>190000</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
+      <c r="A33" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="40">
+      <c r="B33" s="26">
         <v>146000</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="39" t="s">
+      <c r="A34" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="40">
+      <c r="B34" s="26">
         <v>48000</v>
       </c>
     </row>
@@ -4624,420 +4630,443 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
     </row>
     <row r="3" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="114"/>
     </row>
     <row r="4" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
     </row>
     <row r="5" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
     </row>
     <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
     </row>
     <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="112" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="str">
+      <c r="A9" s="27" t="str">
         <f>A7</f>
         <v>🔴</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="111" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
     </row>
     <row r="11" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="111" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
     </row>
     <row r="13" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="str">
+      <c r="A13" s="27" t="str">
         <f>A11</f>
         <v>🔴</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="110" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
     </row>
     <row r="15" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="str">
+      <c r="A15" s="27" t="str">
         <f>A13</f>
         <v>🔴</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="109" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
     </row>
     <row r="17" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="110" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
     </row>
     <row r="19" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+      <c r="B20" s="106"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
     </row>
     <row r="21" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="36" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
     </row>
     <row r="23" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
     </row>
     <row r="24" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="36" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
     </row>
     <row r="26" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
     </row>
     <row r="27" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="51" t="s">
+      <c r="A27" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="D27" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="36" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
     </row>
     <row r="29" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="38"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
     </row>
     <row r="30" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="50" t="s">
+      <c r="E30" s="36" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
     </row>
     <row r="32" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="38"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
     </row>
     <row r="33" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="D33" s="52" t="s">
+      <c r="D33" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="50" t="s">
+      <c r="E33" s="36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
     </row>
     <row r="35" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
     </row>
     <row r="36" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="47" t="s">
+      <c r="B36" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="D36" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="36" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="105"/>
     </row>
     <row r="38" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A20:E20"/>
@@ -5045,29 +5074,6 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5099,477 +5105,477 @@
       <c r="G1" s="116"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="113" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="G3" s="46" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="18">
         <v>670864</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="18">
         <v>859971</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="18">
         <f t="shared" ref="D4:D9" si="0">B4-C4</f>
         <v>-189107</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="21">
         <f t="shared" ref="E4:E20" si="1">IFERROR(D4/ABS(C4),0)</f>
         <v>-0.21989927567324943</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="48" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="9">
         <v>0</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="9">
         <v>0</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F5" s="63" t="s">
+      <c r="F5" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="50" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="9">
         <v>0</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="9">
         <v>0</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F6" s="63" t="s">
+      <c r="F6" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="50" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="9">
         <v>0</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="9">
         <v>0</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F7" s="63" t="s">
+      <c r="F7" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="50" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="9">
         <f>'📋 Raw Data'!E10</f>
         <v>208950</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="9">
         <f>'📋 Raw Data'!J10</f>
         <v>268650</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="9">
         <f t="shared" si="0"/>
         <v>-59700</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="13">
         <f t="shared" si="1"/>
         <v>-0.22222222222222221</v>
       </c>
-      <c r="F8" s="63" t="s">
+      <c r="F8" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="50" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="9">
         <f>'📋 Raw Data'!E11</f>
         <v>60000</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="9">
         <f>'📋 Raw Data'!J11</f>
         <v>85000</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="9">
         <f t="shared" si="0"/>
         <v>-25000</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="13">
         <f t="shared" si="1"/>
         <v>-0.29411764705882354</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="50" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="18">
         <v>900840</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="18">
         <v>1065600</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="18">
         <f>C10-B10</f>
         <v>164760</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="21">
         <f t="shared" si="1"/>
         <v>0.15461711711711712</v>
       </c>
-      <c r="F10" s="65" t="s">
+      <c r="F10" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="48" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="9">
         <f>'📋 Raw Data'!E13</f>
         <v>750960</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="9">
         <f>'📋 Raw Data'!J13</f>
         <v>885000</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="9">
         <f>C11-B11</f>
         <v>134040</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="13">
         <f t="shared" si="1"/>
         <v>0.15145762711864408</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="50" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="9">
         <f>'📋 Raw Data'!E15</f>
         <v>103500</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="9">
         <f>'📋 Raw Data'!J15</f>
         <v>127500</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="9">
         <f>C12-B12</f>
         <v>24000</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="13">
         <f t="shared" si="1"/>
         <v>0.18823529411764706</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="50" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="18">
         <v>-229976</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="18">
         <v>-205629</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="18">
         <f>B13-C13</f>
         <v>-24347</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="21">
         <f t="shared" si="1"/>
         <v>-0.11840255995020157</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="48" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="18">
         <v>1461000</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="18">
         <v>1345000</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="18">
         <f>C14-B14</f>
         <v>-116000</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="21">
         <f t="shared" si="1"/>
         <v>-8.6245353159851296E-2</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="62" t="s">
+      <c r="G14" s="48" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="9">
         <f>'📋 Raw Data'!E19</f>
         <v>195000</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="9">
         <f>'📋 Raw Data'!J19</f>
         <v>180000</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="9">
         <f>C15-B15</f>
         <v>-15000</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="13">
         <f t="shared" si="1"/>
         <v>-8.3333333333333329E-2</v>
       </c>
-      <c r="F15" s="63" t="s">
+      <c r="F15" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="50" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="9">
         <f>'📋 Raw Data'!E20</f>
         <v>115000</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="9">
         <f>'📋 Raw Data'!J20</f>
         <v>90000</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="9">
         <f>C16-B16</f>
         <v>-25000</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="13">
         <f t="shared" si="1"/>
         <v>-0.27777777777777779</v>
       </c>
-      <c r="F16" s="63" t="s">
+      <c r="F16" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="50" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="9">
         <f>'📋 Raw Data'!E22</f>
         <v>270000</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="9">
         <f>'📋 Raw Data'!J22</f>
         <v>225000</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="9">
         <f>C17-B17</f>
         <v>-45000</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="13">
         <f t="shared" si="1"/>
         <v>-0.2</v>
       </c>
-      <c r="F17" s="63" t="s">
+      <c r="F17" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="50" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="9">
         <f>'📋 Raw Data'!E23</f>
         <v>60000</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="9">
         <f>'📋 Raw Data'!J23</f>
         <v>37000</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="9">
         <f>C18-B18</f>
         <v>-23000</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="13">
         <f t="shared" si="1"/>
         <v>-0.6216216216216216</v>
       </c>
-      <c r="F18" s="63" t="s">
+      <c r="F18" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="50" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="18">
         <v>-1690976</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="18">
         <v>-1550629</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="18">
         <f>B19-C19</f>
         <v>-140347</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="21">
         <f t="shared" si="1"/>
         <v>-9.0509722183707383E-2</v>
       </c>
-      <c r="F19" s="61" t="s">
+      <c r="F19" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="48" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="18">
         <v>-1738976</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="18">
         <v>-1598629</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="18">
         <f>B20-C20</f>
         <v>-140347</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="21">
         <f t="shared" si="1"/>
         <v>-8.7792101857278954E-2</v>
       </c>
-      <c r="F20" s="61" t="s">
+      <c r="F20" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="62" t="s">
+      <c r="G20" s="48" t="s">
         <v>147</v>
       </c>
     </row>
@@ -5611,845 +5617,845 @@
       <c r="K1" s="116"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
     </row>
     <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="103" t="s">
         <v>150</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="54" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="J4" s="68" t="s">
+      <c r="J4" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="K4" s="69" t="s">
+      <c r="K4" s="55" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="71">
+      <c r="B5" s="57">
         <f>'📋 Raw Data'!B5</f>
         <v>4680</v>
       </c>
-      <c r="C5" s="71">
+      <c r="C5" s="57">
         <f>'📋 Raw Data'!C5</f>
         <v>4800</v>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="57">
         <f>'📋 Raw Data'!D5</f>
         <v>5980</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="58">
         <f>'📋 Raw Data'!E5</f>
         <v>15460</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="73">
+      <c r="F5" s="6"/>
+      <c r="G5" s="59">
         <f>'📋 Raw Data'!G5</f>
         <v>5460</v>
       </c>
-      <c r="H5" s="73">
+      <c r="H5" s="59">
         <f>'📋 Raw Data'!H5</f>
         <v>5760</v>
       </c>
-      <c r="I5" s="73">
+      <c r="I5" s="59">
         <f>'📋 Raw Data'!I5</f>
         <v>7020</v>
       </c>
-      <c r="J5" s="74">
+      <c r="J5" s="60">
         <f>'📋 Raw Data'!J5</f>
         <v>18240</v>
       </c>
-      <c r="K5" s="75">
+      <c r="K5" s="61">
         <f>IFERROR(B5-G5,0)</f>
         <v>-780</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="9">
         <f>IFERROR('📋 Raw Data'!B7/B5,0)</f>
         <v>4.1997863247863245</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="9">
         <f>IFERROR('📋 Raw Data'!C7/B5,0)</f>
         <v>4.64508547008547</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="9">
         <f>IFERROR('📋 Raw Data'!D7/B5,0)</f>
         <v>5.3418803418803416</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="62">
         <f t="shared" ref="E6:E11" si="0">IFERROR(SUM(B6:D6)/3,0)</f>
         <v>4.7289173789173793</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="25">
+      <c r="F6" s="6"/>
+      <c r="G6" s="11">
         <f>IFERROR('📋 Raw Data'!G7/G5,0)</f>
         <v>4.2214285714285715</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="11">
         <f>IFERROR('📋 Raw Data'!H7/G5,0)</f>
         <v>4.7366300366300367</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="11">
         <f>IFERROR('📋 Raw Data'!I7/G5,0)</f>
         <v>5.4450549450549453</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="11">
         <f t="shared" ref="J6:J11" si="1">IFERROR(SUM(G6:I6)/3,0)</f>
         <v>4.8010378510378509</v>
       </c>
-      <c r="K6" s="77">
+      <c r="K6" s="63">
         <f t="shared" ref="K6:K12" si="2">IFERROR(E6-J6,0)</f>
         <v>-7.2120472120471568E-2</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="9">
         <f>IFERROR('📋 Raw Data'!B7*0.15/1.18/B5,0)</f>
         <v>0.53387114298131255</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="9">
         <f>IFERROR('📋 Raw Data'!C7*0.15/1.18/B5,0)</f>
         <v>0.59047696653628856</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="9">
         <f>IFERROR('📋 Raw Data'!D7*0.15/1.18/B5,0)</f>
         <v>0.67905258583224681</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="62">
         <f t="shared" si="0"/>
         <v>0.60113356511661598</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="25">
+      <c r="F7" s="6"/>
+      <c r="G7" s="11">
         <f>IFERROR('📋 Raw Data'!G7*0.15/1.18/G5,0)</f>
         <v>0.53662227602905577</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="11">
         <f>IFERROR('📋 Raw Data'!H7*0.15/1.18/G5,0)</f>
         <v>0.60211398770720803</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="11">
         <f>IFERROR('📋 Raw Data'!I7*0.15/1.18/G5,0)</f>
         <v>0.69216800149003543</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="11">
         <f t="shared" si="1"/>
         <v>0.61030142174209967</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="63">
         <f t="shared" si="2"/>
         <v>-9.1678566254836946E-3</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="64" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="79">
+      <c r="B8" s="65">
         <f>IFERROR('📋 Raw Data'!B13/B5,0)</f>
         <v>50</v>
       </c>
-      <c r="C8" s="79">
+      <c r="C8" s="65">
         <f>IFERROR('📋 Raw Data'!C13/B5,0)</f>
         <v>51.282051282051285</v>
       </c>
-      <c r="D8" s="79">
+      <c r="D8" s="65">
         <f>IFERROR('📋 Raw Data'!D13/B5,0)</f>
         <v>59.179487179487182</v>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="62">
         <f t="shared" si="0"/>
         <v>53.487179487179482</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="11">
         <f>IFERROR('📋 Raw Data'!G13/G5,0)</f>
         <v>50</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="11">
         <f>IFERROR('📋 Raw Data'!H13/G5,0)</f>
         <v>52.747252747252745</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="11">
         <f>IFERROR('📋 Raw Data'!I13/G5,0)</f>
         <v>59.340659340659343</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="11">
         <f t="shared" si="1"/>
         <v>54.029304029304029</v>
       </c>
-      <c r="K8" s="77">
+      <c r="K8" s="63">
         <f t="shared" si="2"/>
         <v>-0.5421245421245473</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="65">
         <f>IFERROR('📋 Raw Data'!B14/B5,0)</f>
         <v>3</v>
       </c>
-      <c r="C9" s="79">
+      <c r="C9" s="65">
         <f>IFERROR('📋 Raw Data'!C14/B5,0)</f>
         <v>3.0769230769230771</v>
       </c>
-      <c r="D9" s="79">
+      <c r="D9" s="65">
         <f>IFERROR('📋 Raw Data'!D14/B5,0)</f>
         <v>3.8333333333333335</v>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="62">
         <f t="shared" si="0"/>
         <v>3.3034188034188037</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="25">
+      <c r="F9" s="6"/>
+      <c r="G9" s="11">
         <f>IFERROR('📋 Raw Data'!G14/G5,0)</f>
         <v>3</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="11">
         <f>IFERROR('📋 Raw Data'!H14/G5,0)</f>
         <v>3.1648351648351647</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="11">
         <f>IFERROR('📋 Raw Data'!I14/G5,0)</f>
         <v>3.5604395604395602</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="11">
         <f t="shared" si="1"/>
         <v>3.2417582417582413</v>
       </c>
-      <c r="K9" s="77">
+      <c r="K9" s="63">
         <f t="shared" si="2"/>
         <v>6.166056166056233E-2</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="18">
         <f>B7-B8-B9</f>
         <v>-52.466128857018688</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="18">
         <f>C7-C8-C9</f>
         <v>-53.768497392438078</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="18">
         <f>D7-D8-D9</f>
         <v>-62.333767926988273</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="18">
         <f t="shared" si="0"/>
         <v>-56.189464725481685</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="32">
+      <c r="F10" s="6"/>
+      <c r="G10" s="18">
         <f>G7-G8-G9</f>
         <v>-52.463377723970943</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="18">
         <f>H7-H8-H9</f>
         <v>-55.309973924380706</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="18">
         <f>I7-I8-I9</f>
         <v>-62.208930899608866</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="18">
         <f t="shared" si="1"/>
         <v>-56.660760849320177</v>
       </c>
-      <c r="K10" s="80">
+      <c r="K10" s="66">
         <f t="shared" si="2"/>
         <v>0.47129612383849206</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="21">
         <f>IFERROR(B10/B7,0)</f>
         <v>-98.274891885016515</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="21">
         <f>IFERROR(C10/C7,0)</f>
         <v>-91.059432356594158</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="21">
         <f>IFERROR(D10/D7,0)</f>
         <v>-91.795200000000008</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="21">
         <f t="shared" si="0"/>
         <v>-93.709841413870222</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="35">
+      <c r="F11" s="6"/>
+      <c r="G11" s="21">
         <f>IFERROR(G10/G7,0)</f>
         <v>-97.765933446136472</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="21">
         <f>IFERROR(H10/H7,0)</f>
         <v>-91.859639625705668</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="21">
         <f>IFERROR(I10/I7,0)</f>
         <v>-89.875479313824414</v>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="21">
         <f t="shared" si="1"/>
         <v>-93.167017461888861</v>
       </c>
-      <c r="K11" s="81">
+      <c r="K11" s="67">
         <f t="shared" si="2"/>
         <v>-0.54282395198136157</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="83">
+      <c r="B12" s="69">
         <f>IFERROR(('📋 Raw Data'!B17+'📋 Raw Data'!B18+'📋 Raw Data'!B19+'📋 Raw Data'!B20+'📋 Raw Data'!B21+'📋 Raw Data'!B22+'📋 Raw Data'!B23+'📋 Raw Data'!B24+'📋 Raw Data'!B25+'📋 Raw Data'!B26+'📋 Raw Data'!B27)/B10/30,0)</f>
         <v>-294.1580343271072</v>
       </c>
-      <c r="C12" s="83">
+      <c r="C12" s="69">
         <f>IFERROR(('📋 Raw Data'!C17+'📋 Raw Data'!C18+'📋 Raw Data'!C19+'📋 Raw Data'!C20+'📋 Raw Data'!C21+'📋 Raw Data'!C22+'📋 Raw Data'!C23+'📋 Raw Data'!C24+'📋 Raw Data'!C25+'📋 Raw Data'!C26+'📋 Raw Data'!C27)/C10/30,0)</f>
         <v>-298.19195459957632</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="69">
         <f>IFERROR(('📋 Raw Data'!D17+'📋 Raw Data'!D18+'📋 Raw Data'!D19+'📋 Raw Data'!D20+'📋 Raw Data'!D21+'📋 Raw Data'!D22+'📋 Raw Data'!D23+'📋 Raw Data'!D24+'📋 Raw Data'!D25+'📋 Raw Data'!D26+'📋 Raw Data'!D27)/D10/30,0)</f>
         <v>-276.46866067071039</v>
       </c>
-      <c r="E12" s="83">
+      <c r="E12" s="69">
         <f>AVERAGE(B12:D12)</f>
         <v>-289.60621653246466</v>
       </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="83">
+      <c r="F12" s="6"/>
+      <c r="G12" s="69">
         <f>IFERROR(('📋 Raw Data'!G17+'📋 Raw Data'!G18+'📋 Raw Data'!G19+'📋 Raw Data'!G20+'📋 Raw Data'!G21+'📋 Raw Data'!G22+'📋 Raw Data'!G23+'📋 Raw Data'!G24+'📋 Raw Data'!G25+'📋 Raw Data'!G26+'📋 Raw Data'!G27)/G10/30,0)</f>
         <v>-280.19545514858169</v>
       </c>
-      <c r="H12" s="83">
+      <c r="H12" s="69">
         <f>IFERROR(('📋 Raw Data'!H17+'📋 Raw Data'!H18+'📋 Raw Data'!H19+'📋 Raw Data'!H20+'📋 Raw Data'!H21+'📋 Raw Data'!H22+'📋 Raw Data'!H23+'📋 Raw Data'!H24+'📋 Raw Data'!H25+'📋 Raw Data'!H26+'📋 Raw Data'!H27)/H10/30,0)</f>
         <v>-269.99349798555414</v>
       </c>
-      <c r="I12" s="83">
+      <c r="I12" s="69">
         <f>IFERROR(('📋 Raw Data'!I17+'📋 Raw Data'!I18+'📋 Raw Data'!I19+'📋 Raw Data'!I20+'📋 Raw Data'!I21+'📋 Raw Data'!I22+'📋 Raw Data'!I23+'📋 Raw Data'!I24+'📋 Raw Data'!I25+'📋 Raw Data'!I26+'📋 Raw Data'!I27)/I10/30,0)</f>
         <v>-244.33790743855346</v>
       </c>
-      <c r="J12" s="83">
+      <c r="J12" s="69">
         <f>AVERAGE(G12:I12)</f>
         <v>-264.84228685756307</v>
       </c>
-      <c r="K12" s="84">
+      <c r="K12" s="70">
         <f t="shared" si="2"/>
         <v>-24.76392967490159</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="117" t="s">
+      <c r="A14" s="118" t="s">
         <v>166</v>
       </c>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="117"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="4">
         <v>600</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="4">
         <v>750</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="4">
         <v>900</v>
       </c>
-      <c r="E15" s="85">
+      <c r="E15" s="71">
         <f t="shared" ref="E15:E22" si="3">AVERAGE(B15:D15)</f>
         <v>750</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21">
+      <c r="F15" s="6"/>
+      <c r="G15" s="7">
         <v>700</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="7">
         <v>850</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="7">
         <v>1000</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="7">
         <f t="shared" ref="J15:J22" si="4">AVERAGE(G15:I15)</f>
         <v>850</v>
       </c>
-      <c r="K15" s="75">
+      <c r="K15" s="61">
         <f t="shared" ref="K15:K22" si="5">IFERROR(E15-J15,0)</f>
         <v>-100</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="9">
         <v>95000</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="9">
         <v>110000</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="9">
         <v>125000</v>
       </c>
-      <c r="E16" s="76">
+      <c r="E16" s="62">
         <f t="shared" si="3"/>
         <v>110000</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="25">
+      <c r="F16" s="6"/>
+      <c r="G16" s="11">
         <v>80000</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="11">
         <v>87000</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="11">
         <v>95000</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="11">
         <f t="shared" si="4"/>
         <v>87333.333333333328</v>
       </c>
-      <c r="K16" s="77">
+      <c r="K16" s="63">
         <f t="shared" si="5"/>
         <v>22666.666666666672</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="9">
         <v>30000</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="9">
         <v>37500</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="9">
         <v>36000</v>
       </c>
-      <c r="E17" s="76">
+      <c r="E17" s="62">
         <f t="shared" si="3"/>
         <v>34500</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="25">
+      <c r="F17" s="6"/>
+      <c r="G17" s="11">
         <v>35000</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="11">
         <v>42500</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="11">
         <v>50000</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="11">
         <f t="shared" si="4"/>
         <v>42500</v>
       </c>
-      <c r="K17" s="77">
+      <c r="K17" s="63">
         <f t="shared" si="5"/>
         <v>-8000</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="18">
         <v>125000</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="18">
         <v>147500</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="18">
         <v>161000</v>
       </c>
-      <c r="E18" s="86">
+      <c r="E18" s="72">
         <f t="shared" si="3"/>
         <v>144500</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="32">
+      <c r="F18" s="6"/>
+      <c r="G18" s="18">
         <v>207500</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="18">
         <v>214500</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="18">
         <v>222500</v>
       </c>
-      <c r="J18" s="32">
+      <c r="J18" s="18">
         <f t="shared" si="4"/>
         <v>214833.33333333334</v>
       </c>
-      <c r="K18" s="80">
+      <c r="K18" s="66">
         <f t="shared" si="5"/>
         <v>-70333.333333333343</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="18">
         <v>208.3</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="18">
         <v>196.7</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="18">
         <v>178.9</v>
       </c>
-      <c r="E19" s="86">
+      <c r="E19" s="72">
         <f t="shared" si="3"/>
         <v>194.63333333333333</v>
       </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="32">
+      <c r="F19" s="6"/>
+      <c r="G19" s="18">
         <v>214.3</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="18">
         <v>193.5</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="18">
         <v>180</v>
       </c>
-      <c r="J19" s="32">
+      <c r="J19" s="18">
         <f t="shared" si="4"/>
         <v>195.93333333333331</v>
       </c>
-      <c r="K19" s="80">
+      <c r="K19" s="66">
         <f t="shared" si="5"/>
         <v>-1.2999999999999829</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="9">
         <v>749.1</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="9">
         <v>744.1</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="9">
         <v>744.1</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="62">
         <f t="shared" si="3"/>
         <v>745.76666666666677</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="25">
+      <c r="F20" s="6"/>
+      <c r="G20" s="11">
         <v>806.1</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="11">
         <v>819.9</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="11">
         <v>888.8</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="11">
         <f t="shared" si="4"/>
         <v>838.26666666666677</v>
       </c>
-      <c r="K20" s="77">
+      <c r="K20" s="63">
         <f t="shared" si="5"/>
         <v>-92.5</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="9">
         <v>8989</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="9">
         <v>8929</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="9">
         <v>8929</v>
       </c>
-      <c r="E21" s="76">
+      <c r="E21" s="62">
         <f t="shared" si="3"/>
         <v>8949</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="25">
+      <c r="F21" s="6"/>
+      <c r="G21" s="11">
         <v>9673</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="11">
         <v>9839</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="11">
         <v>10665</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="11">
         <f t="shared" si="4"/>
         <v>10059</v>
       </c>
-      <c r="K21" s="77">
+      <c r="K21" s="63">
         <f t="shared" si="5"/>
         <v>-1110</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="87">
+      <c r="B22" s="73">
         <v>43.15</v>
       </c>
-      <c r="C22" s="87">
+      <c r="C22" s="73">
         <v>45.4</v>
       </c>
-      <c r="D22" s="87">
+      <c r="D22" s="73">
         <v>49.91</v>
       </c>
-      <c r="E22" s="88">
+      <c r="E22" s="74">
         <f t="shared" si="3"/>
         <v>46.153333333333329</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="87">
+      <c r="F22" s="6"/>
+      <c r="G22" s="73">
         <v>45.14</v>
       </c>
-      <c r="H22" s="87">
+      <c r="H22" s="73">
         <v>50.84</v>
       </c>
-      <c r="I22" s="87">
+      <c r="I22" s="73">
         <v>59.25</v>
       </c>
-      <c r="J22" s="87">
+      <c r="J22" s="73">
         <f t="shared" si="4"/>
         <v>51.743333333333339</v>
       </c>
-      <c r="K22" s="89">
+      <c r="K22" s="75">
         <f t="shared" si="5"/>
         <v>-5.5900000000000105</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
     </row>
     <row r="25" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="118" t="s">
+      <c r="A25" s="119" t="s">
         <v>175</v>
       </c>
-      <c r="B25" s="118"/>
-      <c r="C25" s="118"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="118"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="118"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
     </row>
     <row r="26" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="76" t="s">
         <v>176</v>
       </c>
-      <c r="B26" s="119" t="s">
+      <c r="B26" s="117" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="119"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
     </row>
     <row r="27" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="90" t="s">
+      <c r="A27" s="76" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="119" t="s">
+      <c r="B27" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="117"/>
     </row>
     <row r="28" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="B28" s="119" t="s">
+      <c r="B28" s="117" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
     </row>
     <row r="29" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="90" t="s">
+      <c r="A29" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="119" t="s">
+      <c r="B29" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="119"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="117"/>
+      <c r="I29" s="117"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="117"/>
     </row>
     <row r="30" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="90" t="s">
+      <c r="A30" s="76" t="s">
         <v>184</v>
       </c>
-      <c r="B30" s="119" t="s">
+      <c r="B30" s="117" t="s">
         <v>185</v>
       </c>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="B26:K26"/>
     <mergeCell ref="B27:K27"/>
     <mergeCell ref="B28:K28"/>
     <mergeCell ref="B29:K29"/>
     <mergeCell ref="B30:K30"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A25:K25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6462,7 +6468,10 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="6" width="15" customWidth="1"/>
+    <col min="2" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6476,740 +6485,740 @@
       <c r="F1" s="116"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="113" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="91" t="s">
+      <c r="A3" s="77" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="79" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="94" t="s">
+      <c r="D3" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="81" t="s">
         <v>192</v>
       </c>
-      <c r="F3" s="96" t="s">
+      <c r="F3" s="82" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="119" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="B5" s="83">
+        <v>250</v>
+      </c>
+      <c r="C5" s="83">
+        <v>350</v>
+      </c>
+      <c r="D5" s="83">
+        <v>150</v>
+      </c>
+      <c r="E5" s="84">
+        <v>203</v>
+      </c>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="97">
-        <v>250</v>
-      </c>
-      <c r="C5" s="97">
+      <c r="B6" s="85">
+        <v>155</v>
+      </c>
+      <c r="C6" s="85">
+        <v>160</v>
+      </c>
+      <c r="D6" s="85">
+        <v>145</v>
+      </c>
+      <c r="E6" s="86">
+        <v>4</v>
+      </c>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="87">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="87">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="87">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E7" s="88">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="83">
+        <v>8</v>
+      </c>
+      <c r="C8" s="83">
+        <v>12</v>
+      </c>
+      <c r="D8" s="83">
+        <v>5</v>
+      </c>
+      <c r="E8" s="89">
+        <v>5</v>
+      </c>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="85">
+        <v>26000</v>
+      </c>
+      <c r="C9" s="85">
+        <v>32000</v>
+      </c>
+      <c r="D9" s="85">
+        <v>22000</v>
+      </c>
+      <c r="E9" s="86">
+        <v>21600</v>
+      </c>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="83">
+        <v>550</v>
+      </c>
+      <c r="C10" s="83">
+        <v>800</v>
+      </c>
+      <c r="D10" s="83">
         <v>350</v>
       </c>
-      <c r="D5" s="97">
-        <v>150</v>
-      </c>
-      <c r="E5" s="98">
+      <c r="E10" s="84">
+        <v>350</v>
+      </c>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B11" s="85">
+        <v>199</v>
+      </c>
+      <c r="C11" s="85">
+        <v>199</v>
+      </c>
+      <c r="D11" s="85">
+        <v>179</v>
+      </c>
+      <c r="E11" s="86">
+        <v>199</v>
+      </c>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="85">
+        <v>28000</v>
+      </c>
+      <c r="C12" s="85">
+        <v>40000</v>
+      </c>
+      <c r="D12" s="85">
+        <v>18000</v>
+      </c>
+      <c r="E12" s="86">
+        <v>20000</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="85">
+        <v>45</v>
+      </c>
+      <c r="C13" s="85">
+        <v>48</v>
+      </c>
+      <c r="D13" s="85">
+        <v>42</v>
+      </c>
+      <c r="E13" s="86">
+        <v>49</v>
+      </c>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F5" s="20"/>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="99">
-        <v>155</v>
-      </c>
-      <c r="C6" s="99">
-        <v>160</v>
-      </c>
-      <c r="D6" s="99">
-        <v>145</v>
-      </c>
-      <c r="E6" s="100">
-        <v>4</v>
-      </c>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B7" s="101">
-        <v>0.15</v>
-      </c>
-      <c r="C7" s="101">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="101">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E7" s="102">
-        <v>0</v>
-      </c>
-      <c r="F7" s="20"/>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="97">
-        <v>8</v>
-      </c>
-      <c r="C8" s="97">
-        <v>12</v>
-      </c>
-      <c r="D8" s="97">
-        <v>5</v>
-      </c>
-      <c r="E8" s="103">
-        <v>5</v>
-      </c>
-      <c r="F8" s="20"/>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="99">
-        <v>26000</v>
-      </c>
-      <c r="C9" s="99">
-        <v>32000</v>
-      </c>
-      <c r="D9" s="99">
-        <v>22000</v>
-      </c>
-      <c r="E9" s="100">
-        <v>21600</v>
-      </c>
-      <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="B10" s="97">
-        <v>550</v>
-      </c>
-      <c r="C10" s="97">
-        <v>800</v>
-      </c>
-      <c r="D10" s="97">
-        <v>350</v>
-      </c>
-      <c r="E10" s="98">
-        <v>350</v>
-      </c>
-      <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" s="99">
-        <v>199</v>
-      </c>
-      <c r="C11" s="99">
-        <v>199</v>
-      </c>
-      <c r="D11" s="99">
-        <v>179</v>
-      </c>
-      <c r="E11" s="100">
-        <v>199</v>
-      </c>
-      <c r="F11" s="20"/>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" s="99">
-        <v>28000</v>
-      </c>
-      <c r="C12" s="99">
-        <v>40000</v>
-      </c>
-      <c r="D12" s="99">
-        <v>18000</v>
-      </c>
-      <c r="E12" s="100">
-        <v>20000</v>
-      </c>
-      <c r="F12" s="20"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="99">
-        <v>45</v>
-      </c>
-      <c r="C13" s="99">
-        <v>48</v>
-      </c>
-      <c r="D13" s="99">
-        <v>42</v>
-      </c>
-      <c r="E13" s="100">
-        <v>49</v>
-      </c>
-      <c r="F13" s="20"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="B14" s="85">
+        <v>90000</v>
+      </c>
+      <c r="C14" s="85">
+        <v>120000</v>
+      </c>
+      <c r="D14" s="85">
+        <v>70000</v>
+      </c>
+      <c r="E14" s="86">
+        <v>110000</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="99">
-        <v>90000</v>
-      </c>
-      <c r="C14" s="99">
-        <v>120000</v>
-      </c>
-      <c r="D14" s="99">
-        <v>70000</v>
-      </c>
-      <c r="E14" s="100">
-        <v>110000</v>
-      </c>
-      <c r="F14" s="20"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="83">
+        <v>26</v>
+      </c>
+      <c r="C15" s="83">
+        <v>26</v>
+      </c>
+      <c r="D15" s="83">
+        <v>24</v>
+      </c>
+      <c r="E15" s="89">
+        <v>25</v>
+      </c>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+    </row>
+    <row r="17" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="114" t="s">
         <v>205</v>
       </c>
-      <c r="B15" s="97">
-        <v>26</v>
-      </c>
-      <c r="C15" s="97">
-        <v>26</v>
-      </c>
-      <c r="D15" s="97">
-        <v>24</v>
-      </c>
-      <c r="E15" s="103">
-        <v>25</v>
-      </c>
-      <c r="F15" s="20"/>
-    </row>
-    <row r="16" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-    </row>
-    <row r="17" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="B17" s="114"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="18">
+      <c r="B18" s="4">
         <f>B5*B15</f>
         <v>6500</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="4">
         <f>C5*C15</f>
         <v>9100</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="4">
         <f>D5*D15</f>
         <v>3600</v>
       </c>
-      <c r="E18" s="104">
+      <c r="E18" s="90">
         <f>E5*E15</f>
         <v>5075</v>
       </c>
-      <c r="F18" s="20"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="18">
         <f>IFERROR(B5*B15*B6*B7/1.18+B9*B10*0.9+B11*B12+B13,0)</f>
         <v>18570117.033898305</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="18">
         <f>IFERROR(C5*C15*C6*C7/1.18+C9*C10*0.9+C11*C12+C13,0)</f>
         <v>31185132.745762713</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="18">
         <f>IFERROR(D5*D15*D6*D7/1.18+D9*D10*0.9+D11*D12+D13,0)</f>
         <v>10213974.203389831</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="18">
         <f>IFERROR(E5*E15*E6*E7/1.18+E9*E10*0.9+E11*E12+E13,0)</f>
         <v>10784049</v>
       </c>
-      <c r="F19" s="80">
+      <c r="F19" s="66">
         <f>IFERROR(B19-E19,0)</f>
         <v>7786068.0338983051</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="9">
         <f>IFERROR(B5*B15*B6*B7/1.18,0)</f>
         <v>128072.03389830509</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="9">
         <f>IFERROR(C5*C15*C6*C7/1.18,0)</f>
         <v>185084.74576271189</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="9">
         <f>IFERROR(D5*D15*D6*D7/1.18,0)</f>
         <v>61932.203389830509</v>
       </c>
-      <c r="E20" s="105">
+      <c r="E20" s="91">
         <f>IFERROR(E5*E15*E6*E7/1.18,0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="20"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B21" s="23">
+      <c r="A21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="9">
         <f>IFERROR(B9*B10*0.9,0)</f>
         <v>12870000</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="9">
         <f>IFERROR(C9*C10*0.9,0)</f>
         <v>23040000</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="9">
         <f>IFERROR(D9*D10*0.9,0)</f>
         <v>6930000</v>
       </c>
-      <c r="E21" s="105">
+      <c r="E21" s="91">
         <f>IFERROR(E9*E10*0.9,0)</f>
         <v>6804000</v>
       </c>
-      <c r="F21" s="20"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="B22" s="23">
+      <c r="A22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B22" s="9">
         <f>IFERROR(B11*B12,0)</f>
         <v>5572000</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="9">
         <f>IFERROR(C11*C12,0)</f>
         <v>7960000</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="9">
         <f>IFERROR(D11*D12,0)</f>
         <v>3222000</v>
       </c>
-      <c r="E22" s="105">
+      <c r="E22" s="91">
         <f>IFERROR(E11*E12,0)</f>
         <v>3980000</v>
       </c>
-      <c r="F22" s="20"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="B23" s="23">
+      <c r="A23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="9">
         <f>IFERROR(B13,0)</f>
         <v>45</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="9">
         <f>IFERROR(C13,0)</f>
         <v>48</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="9">
         <f>IFERROR(D13,0)</f>
         <v>42</v>
       </c>
-      <c r="E23" s="105">
+      <c r="E23" s="91">
         <f>IFERROR(E13,0)</f>
         <v>49</v>
       </c>
-      <c r="F23" s="20"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="A24" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" s="18">
         <f>IFERROR(B5*B15*(B14+3)+600*50,0)</f>
         <v>585049500</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="18">
         <f>IFERROR(C5*C15*(C14+3)+600*50,0)</f>
         <v>1092057300</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="18">
         <f>IFERROR(D5*D15*(D14+3)+600*50,0)</f>
         <v>252040800</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="18">
         <f>IFERROR(E5*E15*(E14+3)+600*50,0)</f>
         <v>558295225</v>
       </c>
-      <c r="F24" s="80">
+      <c r="F24" s="66">
         <f>IFERROR(B24-E24,0)</f>
         <v>26754275</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="9">
         <f>IFERROR(B5*B15*B14,0)</f>
         <v>585000000</v>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="9">
         <f>IFERROR(C5*C15*C14,0)</f>
         <v>1092000000</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="9">
         <f>IFERROR(D5*D15*D14,0)</f>
         <v>252000000</v>
       </c>
-      <c r="E25" s="105">
+      <c r="E25" s="91">
         <f>IFERROR(E5*E15*E14,0)</f>
         <v>558250000</v>
       </c>
-      <c r="F25" s="20"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B26" s="23">
+      <c r="A26" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" s="9">
         <f>IFERROR(B5*B15*3+600*50,0)</f>
         <v>49500</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="9">
         <f>IFERROR(C5*C15*3+600*50,0)</f>
         <v>57300</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="9">
         <f>IFERROR(D5*D15*3+600*50,0)</f>
         <v>40800</v>
       </c>
-      <c r="E26" s="105">
+      <c r="E26" s="91">
         <f>IFERROR(E5*E15*3+600*50,0)</f>
         <v>45225</v>
       </c>
-      <c r="F26" s="20"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="18">
         <f>IFERROR(B25-B24,0)</f>
         <v>-49500</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="18">
         <f>IFERROR(C25-C24,0)</f>
         <v>-57300</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="18">
         <f>IFERROR(D25-D24,0)</f>
         <v>-40800</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="18">
         <f>IFERROR(E25-E24,0)</f>
         <v>-45225</v>
       </c>
-      <c r="F27" s="80">
+      <c r="F27" s="66">
         <f>IFERROR(B27-E27,0)</f>
         <v>-4275</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="18">
         <f>IFERROR(275000+B5*60+B20,0)</f>
         <v>418072.03389830509</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="18">
         <f>IFERROR(275000+C5*60+C20,0)</f>
         <v>481084.74576271186</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="18">
         <f>IFERROR(275000+D5*60+D20,0)</f>
         <v>345932.20338983054</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="18">
         <f>IFERROR(275000+E5*60+E20,0)</f>
         <v>287180</v>
       </c>
-      <c r="F28" s="80">
+      <c r="F28" s="66">
         <f>IFERROR(B28-E28,0)</f>
         <v>130892.03389830509</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="23">
+      <c r="A29" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" s="9">
         <f>275000</f>
         <v>275000</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="9">
         <f>275000</f>
         <v>275000</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="9">
         <f>275000</f>
         <v>275000</v>
       </c>
-      <c r="E29" s="105">
+      <c r="E29" s="91">
         <f>275000</f>
         <v>275000</v>
       </c>
-      <c r="F29" s="20"/>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30" s="23">
+      <c r="A30" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B30" s="9">
         <f>IFERROR(B5*60,0)</f>
         <v>15000</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="9">
         <f>IFERROR(C5*60,0)</f>
         <v>21000</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="9">
         <f>IFERROR(D5*60,0)</f>
         <v>9000</v>
       </c>
-      <c r="E30" s="105">
+      <c r="E30" s="91">
         <f>IFERROR(E5*60,0)</f>
         <v>12180</v>
       </c>
-      <c r="F30" s="20"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="A31" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B31" s="9">
         <f>IFERROR(B20,0)</f>
         <v>128072.03389830509</v>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="9">
         <f>IFERROR(C20,0)</f>
         <v>185084.74576271189</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="9">
         <f>IFERROR(D20,0)</f>
         <v>61932.203389830509</v>
       </c>
-      <c r="E31" s="105">
+      <c r="E31" s="91">
         <f>IFERROR(E20,0)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="20"/>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B32" s="23">
+      <c r="A32" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B32" s="9">
         <f>75000</f>
         <v>75000</v>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="9">
         <f>75000</f>
         <v>75000</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="9">
         <f>75000</f>
         <v>75000</v>
       </c>
-      <c r="E32" s="105">
+      <c r="E32" s="91">
         <f>75000</f>
         <v>75000</v>
       </c>
-      <c r="F32" s="20"/>
+      <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="18">
         <f>B27-B28</f>
         <v>-467572.03389830509</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="18">
         <f>C27-C28</f>
         <v>-538384.74576271186</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="18">
         <f>D27-D28</f>
         <v>-386732.20338983054</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="18">
         <f>E27-E28</f>
         <v>-332405</v>
       </c>
-      <c r="F33" s="80">
+      <c r="F33" s="66">
         <f>IFERROR(B33-E33,0)</f>
         <v>-135167.03389830509</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="9">
         <f>16000</f>
         <v>16000</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="9">
         <f>16000</f>
         <v>16000</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="9">
         <f>16000</f>
         <v>16000</v>
       </c>
-      <c r="E34" s="105">
+      <c r="E34" s="91">
         <f>16000</f>
         <v>16000</v>
       </c>
-      <c r="F34" s="20"/>
+      <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="18">
         <f>B33-B34</f>
         <v>-483572.03389830509</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="18">
         <f>C33-C34</f>
         <v>-554384.74576271186</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="18">
         <f>D33-D34</f>
         <v>-402732.20338983054</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="18">
         <f>E33-E34</f>
         <v>-348405</v>
       </c>
-      <c r="F35" s="80">
+      <c r="F35" s="66">
         <f>IFERROR(B35-E35,0)</f>
         <v>-135167.03389830509</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="118" t="s">
+      <c r="A37" s="119" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="119"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="119"/>
+    </row>
+    <row r="38" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="92" t="s">
         <v>217</v>
       </c>
-      <c r="B37" s="118"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-    </row>
-    <row r="38" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="106" t="s">
+      <c r="B38" s="117" t="s">
         <v>218</v>
       </c>
-      <c r="B38" s="119" t="s">
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+    </row>
+    <row r="39" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="119"/>
-    </row>
-    <row r="39" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="107" t="s">
+      <c r="B39" s="117" t="s">
         <v>220</v>
       </c>
-      <c r="B39" s="119" t="s">
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="117"/>
+    </row>
+    <row r="40" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="94" t="s">
         <v>221</v>
       </c>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
-    </row>
-    <row r="40" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="108" t="s">
+      <c r="B40" s="117" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="119" t="s">
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+    </row>
+    <row r="41" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="95" t="s">
         <v>223</v>
       </c>
-      <c r="C40" s="119"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="119"/>
-    </row>
-    <row r="41" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="109" t="s">
+      <c r="B41" s="117" t="s">
         <v>224</v>
       </c>
-      <c r="B41" s="119" t="s">
-        <v>225</v>
-      </c>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="119"/>
+      <c r="C41" s="117"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -7243,7 +7252,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="116" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B1" s="116"/>
       <c r="C1" s="116"/>
@@ -7256,819 +7265,819 @@
       <c r="J1" s="116"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="113" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="B3" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="C3" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="D3" s="52" t="s">
         <v>230</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="E3" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="40" t="s">
         <v>232</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="54" t="s">
+      <c r="H3" s="40" t="s">
         <v>233</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="I3" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="I3" s="54" t="s">
+      <c r="J3" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="J3" s="68" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="96" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="110" t="s">
-        <v>237</v>
-      </c>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="97">
+      <c r="B5" s="83">
         <v>4680</v>
       </c>
-      <c r="C5" s="97">
+      <c r="C5" s="83">
         <v>4800</v>
       </c>
-      <c r="D5" s="97">
+      <c r="D5" s="83">
         <v>5980</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="58">
         <f>SUM(B5:D5)</f>
         <v>15460</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="112">
+      <c r="F5" s="6"/>
+      <c r="G5" s="98">
         <v>5460</v>
       </c>
-      <c r="H5" s="112">
+      <c r="H5" s="98">
         <v>5760</v>
       </c>
-      <c r="I5" s="112">
+      <c r="I5" s="98">
         <v>7020</v>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="58">
         <f>SUM(G5:I5)</f>
         <v>18240</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="96" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="56" t="s">
         <v>238</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="99">
+      <c r="B7" s="85">
         <v>19655</v>
       </c>
-      <c r="C7" s="99">
+      <c r="C7" s="85">
         <v>21739</v>
       </c>
-      <c r="D7" s="99">
+      <c r="D7" s="85">
         <v>25000</v>
       </c>
-      <c r="E7" s="113">
+      <c r="E7" s="99">
         <f>SUM(B7:D7)</f>
         <v>66394</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="114">
+      <c r="F7" s="6"/>
+      <c r="G7" s="100">
         <v>23049</v>
       </c>
-      <c r="H7" s="114">
+      <c r="H7" s="100">
         <v>25862</v>
       </c>
-      <c r="I7" s="114">
+      <c r="I7" s="100">
         <v>29730</v>
       </c>
-      <c r="J7" s="113">
+      <c r="J7" s="99">
         <f>SUM(G7:I7)</f>
         <v>78641</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
-        <v>240</v>
-      </c>
-      <c r="B8" s="99">
+      <c r="A8" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="85">
         <v>0</v>
       </c>
-      <c r="C8" s="99">
+      <c r="C8" s="85">
         <v>3840</v>
       </c>
-      <c r="D8" s="99">
+      <c r="D8" s="85">
         <v>7680</v>
       </c>
-      <c r="E8" s="113">
+      <c r="E8" s="99">
         <f>SUM(B8:D8)</f>
         <v>11520</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="114">
+      <c r="F8" s="6"/>
+      <c r="G8" s="100">
         <v>0</v>
       </c>
-      <c r="H8" s="114">
+      <c r="H8" s="100">
         <v>5760</v>
       </c>
-      <c r="I8" s="114">
+      <c r="I8" s="100">
         <v>11520</v>
       </c>
-      <c r="J8" s="113">
+      <c r="J8" s="99">
         <f>SUM(G8:I8)</f>
         <v>17280</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="70" t="s">
-        <v>241</v>
-      </c>
-      <c r="B9" s="99">
+      <c r="A9" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" s="85">
         <v>86400</v>
       </c>
-      <c r="C9" s="99">
+      <c r="C9" s="85">
         <v>108000</v>
       </c>
-      <c r="D9" s="99">
+      <c r="D9" s="85">
         <v>129600</v>
       </c>
-      <c r="E9" s="113">
+      <c r="E9" s="99">
         <f>SUM(B9:D9)</f>
         <v>324000</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="114">
+      <c r="F9" s="6"/>
+      <c r="G9" s="100">
         <v>108000</v>
       </c>
-      <c r="H9" s="114">
+      <c r="H9" s="100">
         <v>129600</v>
       </c>
-      <c r="I9" s="114">
+      <c r="I9" s="100">
         <v>172800</v>
       </c>
-      <c r="J9" s="113">
+      <c r="J9" s="99">
         <f>SUM(G9:I9)</f>
         <v>410400</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70" t="s">
-        <v>242</v>
-      </c>
-      <c r="B10" s="99">
+      <c r="A10" s="56" t="s">
+        <v>241</v>
+      </c>
+      <c r="B10" s="85">
         <v>55720</v>
       </c>
-      <c r="C10" s="99">
+      <c r="C10" s="85">
         <v>69650</v>
       </c>
-      <c r="D10" s="99">
+      <c r="D10" s="85">
         <v>83580</v>
       </c>
-      <c r="E10" s="113">
+      <c r="E10" s="99">
         <f>SUM(B10:D10)</f>
         <v>208950</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="114">
+      <c r="F10" s="6"/>
+      <c r="G10" s="100">
         <v>69650</v>
       </c>
-      <c r="H10" s="114">
+      <c r="H10" s="100">
         <v>89550</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="100">
         <v>109450</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="99">
         <f>SUM(G10:I10)</f>
         <v>268650</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="B11" s="99">
+      <c r="A11" s="56" t="s">
+        <v>242</v>
+      </c>
+      <c r="B11" s="85">
         <v>18000</v>
       </c>
-      <c r="C11" s="99">
+      <c r="C11" s="85">
         <v>20000</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="85">
         <v>22000</v>
       </c>
-      <c r="E11" s="113">
+      <c r="E11" s="99">
         <f>SUM(B11:D11)</f>
         <v>60000</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="114">
+      <c r="F11" s="6"/>
+      <c r="G11" s="100">
         <v>25000</v>
       </c>
-      <c r="H11" s="114">
+      <c r="H11" s="100">
         <v>28000</v>
       </c>
-      <c r="I11" s="114">
+      <c r="I11" s="100">
         <v>32000</v>
       </c>
-      <c r="J11" s="113">
+      <c r="J11" s="99">
         <f>SUM(G11:I11)</f>
         <v>85000</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="110" t="s">
-        <v>244</v>
-      </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
+      <c r="A12" s="96" t="s">
+        <v>243</v>
+      </c>
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="99">
+      <c r="B13" s="85">
         <v>234000</v>
       </c>
-      <c r="C13" s="99">
+      <c r="C13" s="85">
         <v>240000</v>
       </c>
-      <c r="D13" s="99">
+      <c r="D13" s="85">
         <v>276960</v>
       </c>
-      <c r="E13" s="113">
+      <c r="E13" s="99">
         <f>SUM(B13:D13)</f>
         <v>750960</v>
       </c>
-      <c r="F13" s="20"/>
-      <c r="G13" s="114">
+      <c r="F13" s="6"/>
+      <c r="G13" s="100">
         <v>273000</v>
       </c>
-      <c r="H13" s="114">
+      <c r="H13" s="100">
         <v>288000</v>
       </c>
-      <c r="I13" s="114">
+      <c r="I13" s="100">
         <v>324000</v>
       </c>
-      <c r="J13" s="113">
+      <c r="J13" s="99">
         <f>SUM(G13:I13)</f>
         <v>885000</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" s="99">
+      <c r="A14" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="B14" s="85">
         <v>14040</v>
       </c>
-      <c r="C14" s="99">
+      <c r="C14" s="85">
         <v>14400</v>
       </c>
-      <c r="D14" s="99">
+      <c r="D14" s="85">
         <v>17940</v>
       </c>
-      <c r="E14" s="113">
+      <c r="E14" s="99">
         <f>SUM(B14:D14)</f>
         <v>46380</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="114">
+      <c r="F14" s="6"/>
+      <c r="G14" s="100">
         <v>16380</v>
       </c>
-      <c r="H14" s="114">
+      <c r="H14" s="100">
         <v>17280</v>
       </c>
-      <c r="I14" s="114">
+      <c r="I14" s="100">
         <v>19440</v>
       </c>
-      <c r="J14" s="113">
+      <c r="J14" s="99">
         <f>SUM(G14:I14)</f>
         <v>53100</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="70" t="s">
-        <v>246</v>
-      </c>
-      <c r="B15" s="99">
+      <c r="A15" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="B15" s="85">
         <v>30000</v>
       </c>
-      <c r="C15" s="99">
+      <c r="C15" s="85">
         <v>37500</v>
       </c>
-      <c r="D15" s="99">
+      <c r="D15" s="85">
         <v>36000</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E15" s="99">
         <f>SUM(B15:D15)</f>
         <v>103500</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="114">
+      <c r="F15" s="6"/>
+      <c r="G15" s="100">
         <v>35000</v>
       </c>
-      <c r="H15" s="114">
+      <c r="H15" s="100">
         <v>42500</v>
       </c>
-      <c r="I15" s="114">
+      <c r="I15" s="100">
         <v>50000</v>
       </c>
-      <c r="J15" s="113">
+      <c r="J15" s="99">
         <f>SUM(G15:I15)</f>
         <v>127500</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="110" t="s">
+      <c r="A16" s="96" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="97"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="97"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="70" t="s">
-        <v>248</v>
-      </c>
-      <c r="B17" s="99">
+      <c r="B17" s="85">
         <v>120000</v>
       </c>
-      <c r="C17" s="99">
+      <c r="C17" s="85">
         <v>120000</v>
       </c>
-      <c r="D17" s="99">
+      <c r="D17" s="85">
         <v>120000</v>
       </c>
-      <c r="E17" s="113">
+      <c r="E17" s="99">
         <f t="shared" ref="E17:E27" si="0">SUM(B17:D17)</f>
         <v>360000</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="114">
+      <c r="F17" s="6"/>
+      <c r="G17" s="100">
         <v>120000</v>
       </c>
-      <c r="H17" s="114">
+      <c r="H17" s="100">
         <v>120000</v>
       </c>
-      <c r="I17" s="114">
+      <c r="I17" s="100">
         <v>120000</v>
       </c>
-      <c r="J17" s="113">
+      <c r="J17" s="99">
         <f t="shared" ref="J17:J27" si="1">SUM(G17:I17)</f>
         <v>360000</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="70" t="s">
-        <v>249</v>
-      </c>
-      <c r="B18" s="99">
+      <c r="A18" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="85">
         <v>80000</v>
       </c>
-      <c r="C18" s="99">
+      <c r="C18" s="85">
         <v>80000</v>
       </c>
-      <c r="D18" s="99">
+      <c r="D18" s="85">
         <v>80000</v>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="99">
         <f t="shared" si="0"/>
         <v>240000</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="114">
+      <c r="F18" s="6"/>
+      <c r="G18" s="100">
         <v>80000</v>
       </c>
-      <c r="H18" s="114">
+      <c r="H18" s="100">
         <v>80000</v>
       </c>
-      <c r="I18" s="114">
+      <c r="I18" s="100">
         <v>80000</v>
       </c>
-      <c r="J18" s="113">
+      <c r="J18" s="99">
         <f t="shared" si="1"/>
         <v>240000</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="70" t="s">
-        <v>250</v>
-      </c>
-      <c r="B19" s="99">
+      <c r="A19" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="B19" s="85">
         <v>60000</v>
       </c>
-      <c r="C19" s="99">
+      <c r="C19" s="85">
         <v>60000</v>
       </c>
-      <c r="D19" s="99">
+      <c r="D19" s="85">
         <v>75000</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E19" s="99">
         <f t="shared" si="0"/>
         <v>195000</v>
       </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="114">
+      <c r="F19" s="6"/>
+      <c r="G19" s="100">
         <v>60000</v>
       </c>
-      <c r="H19" s="114">
+      <c r="H19" s="100">
         <v>60000</v>
       </c>
-      <c r="I19" s="114">
+      <c r="I19" s="100">
         <v>60000</v>
       </c>
-      <c r="J19" s="113">
+      <c r="J19" s="99">
         <f t="shared" si="1"/>
         <v>180000</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
-        <v>251</v>
-      </c>
-      <c r="B20" s="99">
+      <c r="A20" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="B20" s="85">
         <v>35000</v>
       </c>
-      <c r="C20" s="99">
+      <c r="C20" s="85">
         <v>38000</v>
       </c>
-      <c r="D20" s="99">
+      <c r="D20" s="85">
         <v>42000</v>
       </c>
-      <c r="E20" s="113">
+      <c r="E20" s="99">
         <f t="shared" si="0"/>
         <v>115000</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="114">
+      <c r="F20" s="6"/>
+      <c r="G20" s="100">
         <v>30000</v>
       </c>
-      <c r="H20" s="114">
+      <c r="H20" s="100">
         <v>30000</v>
       </c>
-      <c r="I20" s="114">
+      <c r="I20" s="100">
         <v>30000</v>
       </c>
-      <c r="J20" s="113">
+      <c r="J20" s="99">
         <f t="shared" si="1"/>
         <v>90000</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="70" t="s">
-        <v>252</v>
-      </c>
-      <c r="B21" s="99">
+      <c r="A21" s="56" t="s">
+        <v>251</v>
+      </c>
+      <c r="B21" s="85">
         <v>25000</v>
       </c>
-      <c r="C21" s="99">
+      <c r="C21" s="85">
         <v>25000</v>
       </c>
-      <c r="D21" s="99">
+      <c r="D21" s="85">
         <v>25000</v>
       </c>
-      <c r="E21" s="113">
+      <c r="E21" s="99">
         <f t="shared" si="0"/>
         <v>75000</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="114">
+      <c r="F21" s="6"/>
+      <c r="G21" s="100">
         <v>25000</v>
       </c>
-      <c r="H21" s="114">
+      <c r="H21" s="100">
         <v>25000</v>
       </c>
-      <c r="I21" s="114">
+      <c r="I21" s="100">
         <v>25000</v>
       </c>
-      <c r="J21" s="113">
+      <c r="J21" s="99">
         <f t="shared" si="1"/>
         <v>75000</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="70" t="s">
-        <v>253</v>
-      </c>
-      <c r="B22" s="99">
+      <c r="A22" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="85">
         <v>80000</v>
       </c>
-      <c r="C22" s="99">
+      <c r="C22" s="85">
         <v>90000</v>
       </c>
-      <c r="D22" s="99">
+      <c r="D22" s="85">
         <v>100000</v>
       </c>
-      <c r="E22" s="113">
+      <c r="E22" s="99">
         <f t="shared" si="0"/>
         <v>270000</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="114">
+      <c r="F22" s="6"/>
+      <c r="G22" s="100">
         <v>70000</v>
       </c>
-      <c r="H22" s="114">
+      <c r="H22" s="100">
         <v>75000</v>
       </c>
-      <c r="I22" s="114">
+      <c r="I22" s="100">
         <v>80000</v>
       </c>
-      <c r="J22" s="113">
+      <c r="J22" s="99">
         <f t="shared" si="1"/>
         <v>225000</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="B23" s="99">
+      <c r="A23" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="85">
         <v>15000</v>
       </c>
-      <c r="C23" s="99">
+      <c r="C23" s="85">
         <v>20000</v>
       </c>
-      <c r="D23" s="99">
+      <c r="D23" s="85">
         <v>25000</v>
       </c>
-      <c r="E23" s="113">
+      <c r="E23" s="99">
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="114">
+      <c r="F23" s="6"/>
+      <c r="G23" s="100">
         <v>10000</v>
       </c>
-      <c r="H23" s="114">
+      <c r="H23" s="100">
         <v>12000</v>
       </c>
-      <c r="I23" s="114">
+      <c r="I23" s="100">
         <v>15000</v>
       </c>
-      <c r="J23" s="113">
+      <c r="J23" s="99">
         <f t="shared" si="1"/>
         <v>37000</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="70" t="s">
-        <v>255</v>
-      </c>
-      <c r="B24" s="99">
+      <c r="A24" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" s="85">
         <v>20000</v>
       </c>
-      <c r="C24" s="99">
+      <c r="C24" s="85">
         <v>20000</v>
       </c>
-      <c r="D24" s="99">
+      <c r="D24" s="85">
         <v>22000</v>
       </c>
-      <c r="E24" s="113">
+      <c r="E24" s="99">
         <f t="shared" si="0"/>
         <v>62000</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="114">
+      <c r="F24" s="6"/>
+      <c r="G24" s="100">
         <v>18000</v>
       </c>
-      <c r="H24" s="114">
+      <c r="H24" s="100">
         <v>18000</v>
       </c>
-      <c r="I24" s="114">
+      <c r="I24" s="100">
         <v>18000</v>
       </c>
-      <c r="J24" s="113">
+      <c r="J24" s="99">
         <f t="shared" si="1"/>
         <v>54000</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="70" t="s">
-        <v>256</v>
-      </c>
-      <c r="B25" s="99">
+      <c r="A25" s="56" t="s">
+        <v>255</v>
+      </c>
+      <c r="B25" s="85">
         <v>15000</v>
       </c>
-      <c r="C25" s="99">
+      <c r="C25" s="85">
         <v>15000</v>
       </c>
-      <c r="D25" s="99">
+      <c r="D25" s="85">
         <v>15000</v>
       </c>
-      <c r="E25" s="113">
+      <c r="E25" s="99">
         <f t="shared" si="0"/>
         <v>45000</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="114">
+      <c r="F25" s="6"/>
+      <c r="G25" s="100">
         <v>15000</v>
       </c>
-      <c r="H25" s="114">
+      <c r="H25" s="100">
         <v>15000</v>
       </c>
-      <c r="I25" s="114">
+      <c r="I25" s="100">
         <v>15000</v>
       </c>
-      <c r="J25" s="113">
+      <c r="J25" s="99">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="70" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="99">
+      <c r="A26" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="85">
         <v>8000</v>
       </c>
-      <c r="C26" s="99">
+      <c r="C26" s="85">
         <v>8000</v>
       </c>
-      <c r="D26" s="99">
+      <c r="D26" s="85">
         <v>8000</v>
       </c>
-      <c r="E26" s="113">
+      <c r="E26" s="99">
         <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="114">
+      <c r="F26" s="6"/>
+      <c r="G26" s="100">
         <v>8000</v>
       </c>
-      <c r="H26" s="114">
+      <c r="H26" s="100">
         <v>8000</v>
       </c>
-      <c r="I26" s="114">
+      <c r="I26" s="100">
         <v>8000</v>
       </c>
-      <c r="J26" s="113">
+      <c r="J26" s="99">
         <f t="shared" si="1"/>
         <v>24000</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
-        <v>258</v>
-      </c>
-      <c r="B27" s="99">
+      <c r="A27" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="B27" s="85">
         <v>5000</v>
       </c>
-      <c r="C27" s="99">
+      <c r="C27" s="85">
         <v>5000</v>
       </c>
-      <c r="D27" s="99">
+      <c r="D27" s="85">
         <v>5000</v>
       </c>
-      <c r="E27" s="113">
+      <c r="E27" s="99">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="114">
+      <c r="F27" s="6"/>
+      <c r="G27" s="100">
         <v>5000</v>
       </c>
-      <c r="H27" s="114">
+      <c r="H27" s="100">
         <v>5000</v>
       </c>
-      <c r="I27" s="114">
+      <c r="I27" s="100">
         <v>5000</v>
       </c>
-      <c r="J27" s="113">
+      <c r="J27" s="99">
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="110" t="s">
+      <c r="A28" s="96" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="B28" s="111"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="70" t="s">
-        <v>260</v>
-      </c>
-      <c r="B29" s="99">
+      <c r="B29" s="85">
         <v>3500</v>
       </c>
-      <c r="C29" s="99">
+      <c r="C29" s="85">
         <v>3500</v>
       </c>
-      <c r="D29" s="99">
+      <c r="D29" s="85">
         <v>3500</v>
       </c>
-      <c r="E29" s="113">
+      <c r="E29" s="99">
         <f>SUM(B29:D29)</f>
         <v>10500</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="114">
+      <c r="F29" s="6"/>
+      <c r="G29" s="100">
         <v>3500</v>
       </c>
-      <c r="H29" s="114">
+      <c r="H29" s="100">
         <v>3500</v>
       </c>
-      <c r="I29" s="114">
+      <c r="I29" s="100">
         <v>3500</v>
       </c>
-      <c r="J29" s="113">
+      <c r="J29" s="99">
         <f>SUM(G29:I29)</f>
         <v>10500</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="B30" s="99">
+      <c r="A30" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="85">
         <v>12500</v>
       </c>
-      <c r="C30" s="99">
+      <c r="C30" s="85">
         <v>12500</v>
       </c>
-      <c r="D30" s="99">
+      <c r="D30" s="85">
         <v>12500</v>
       </c>
-      <c r="E30" s="113">
+      <c r="E30" s="99">
         <f>SUM(B30:D30)</f>
         <v>37500</v>
       </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="114">
+      <c r="F30" s="6"/>
+      <c r="G30" s="100">
         <v>12500</v>
       </c>
-      <c r="H30" s="114">
+      <c r="H30" s="100">
         <v>12500</v>
       </c>
-      <c r="I30" s="114">
+      <c r="I30" s="100">
         <v>12500</v>
       </c>
-      <c r="J30" s="113">
+      <c r="J30" s="99">
         <f>SUM(G30:I30)</f>
         <v>37500</v>
       </c>
@@ -8085,7 +8094,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -8095,207 +8104,183 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="102" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="113"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+    </row>
+    <row r="3" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="103" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+    </row>
+    <row r="4" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-    </row>
-    <row r="3" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="C4" s="125" t="s">
         <v>264</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-    </row>
-    <row r="4" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="47" t="s">
+      <c r="D4" s="125"/>
+    </row>
+    <row r="5" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C5" s="125" t="s">
         <v>266</v>
       </c>
-      <c r="D4" s="120"/>
-    </row>
-    <row r="5" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="47" t="s">
+      <c r="D5" s="125"/>
+    </row>
+    <row r="6" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="120" t="s">
+      <c r="C6" s="125" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="120"/>
-    </row>
-    <row r="6" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="47" t="s">
+      <c r="D6" s="125"/>
+    </row>
+    <row r="7" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="C6" s="120" t="s">
+      <c r="C7" s="125" t="s">
         <v>270</v>
       </c>
-      <c r="D6" s="120"/>
-    </row>
-    <row r="7" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="47" t="s">
+      <c r="D7" s="125"/>
+    </row>
+    <row r="8" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="120" t="s">
+      <c r="C8" s="125" t="s">
         <v>272</v>
       </c>
-      <c r="D7" s="120"/>
-    </row>
-    <row r="8" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
-      <c r="B8" s="47" t="s">
+      <c r="D8" s="125"/>
+    </row>
+    <row r="9" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+    </row>
+    <row r="10" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="106" t="s">
         <v>273</v>
       </c>
-      <c r="C8" s="120" t="s">
+      <c r="B10" s="106"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="106"/>
+    </row>
+    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="101" t="s">
         <v>274</v>
       </c>
-      <c r="D8" s="120"/>
-    </row>
-    <row r="9" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-    </row>
-    <row r="10" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="C11" s="120" t="s">
         <v>275</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
-      <c r="B11" s="115" t="s">
+      <c r="D11" s="120"/>
+    </row>
+    <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="101" t="s">
         <v>276</v>
       </c>
-      <c r="C11" s="121" t="s">
+      <c r="C12" s="123" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="121"/>
-    </row>
-    <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="115" t="s">
+      <c r="D12" s="123"/>
+    </row>
+    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="101" t="s">
         <v>278</v>
       </c>
-      <c r="C12" s="122" t="s">
+      <c r="C13" s="124" t="s">
         <v>279</v>
       </c>
-      <c r="D12" s="122"/>
-    </row>
-    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="115" t="s">
+      <c r="D13" s="124"/>
+    </row>
+    <row r="14" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="101" t="s">
         <v>280</v>
       </c>
-      <c r="C13" s="123" t="s">
+      <c r="C14" s="123" t="s">
         <v>281</v>
       </c>
-      <c r="D13" s="123"/>
-    </row>
-    <row r="14" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="115" t="s">
+      <c r="D14" s="123"/>
+    </row>
+    <row r="15" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="101" t="s">
         <v>282</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C15" s="124" t="s">
         <v>283</v>
       </c>
-      <c r="D14" s="122"/>
-    </row>
-    <row r="15" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="115" t="s">
+      <c r="D15" s="124"/>
+    </row>
+    <row r="16" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="101" t="s">
         <v>284</v>
       </c>
-      <c r="C15" s="123" t="s">
+      <c r="C16" s="121" t="s">
         <v>285</v>
       </c>
-      <c r="D15" s="123"/>
-    </row>
-    <row r="16" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="115" t="s">
+      <c r="D16" s="121"/>
+    </row>
+    <row r="17" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+    </row>
+    <row r="18" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="122" t="s">
         <v>286</v>
       </c>
-      <c r="C16" s="124" t="s">
-        <v>287</v>
-      </c>
-      <c r="D16" s="124"/>
-    </row>
-    <row r="17" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="115" t="s">
-        <v>288</v>
-      </c>
-      <c r="C17" s="121" t="s">
-        <v>289</v>
-      </c>
-      <c r="D17" s="121"/>
-    </row>
-    <row r="18" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="115" t="s">
-        <v>290</v>
-      </c>
-      <c r="C18" s="124" t="s">
-        <v>291</v>
-      </c>
-      <c r="D18" s="124"/>
-    </row>
-    <row r="19" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-    </row>
-    <row r="20" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="125" t="s">
-        <v>292</v>
-      </c>
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A20:D20"/>
+  <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
